--- a/ressources/diametres.xlsx
+++ b/ressources/diametres.xlsx
@@ -1,20 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ecole\TEE\EnRezo\enRezo-Algorithm_steiner_V5.4\ressources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A27BA0FF-2DDF-4014-8669-882BF2FB29A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{7F82A3F0-3E44-46CE-BD27-2987FA7047D6}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Hoja1"/>
+    <sheet name="Final" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Diamètre Nominal (DN)</t>
   </si>
@@ -26,6 +48,9 @@
   </si>
   <si>
     <t>P (MW)</t>
+  </si>
+  <si>
+    <t>Cout (euros/m)</t>
   </si>
   <si>
     <t>DN 20</t>
@@ -73,19 +98,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF1f1f1f"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -98,14 +122,20 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF1f1f1f"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FFff3131"/>
+      <color rgb="FFFF3131"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -118,16 +148,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffe599"/>
+        <fgColor rgb="FFFFE599"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffffff"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -140,13 +170,13 @@
         <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -175,8 +205,8 @@
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFcccccc"/>
+      <bottom style="thin">
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -185,7 +215,35 @@
         <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color rgb="FFcccccc"/>
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="medium">
         <color rgb="FF000000"/>
@@ -199,73 +257,73 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -292,82 +350,116 @@
         <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -379,198 +471,190 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
-            </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E80D5BB7-3607-4563-BA5B-C588F8BE7E89}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="27" customFormat="1" s="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="25.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="6">
         <v>26.9</v>
@@ -581,13 +665,17 @@
       <c r="D2" s="8">
         <v>0.21</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="E2" s="9">
+        <f t="shared" ref="E2:E15" si="0">ROUND(0.0042*B2^2 + 0.2056*B2 + 71.923, 0)</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="6">
-        <v>33.7</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="C3" s="7">
         <v>509.01</v>
@@ -595,10 +683,14 @@
       <c r="D3" s="8">
         <v>0.33</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="E3" s="9">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="6">
         <v>42.4</v>
@@ -609,24 +701,32 @@
       <c r="D4" s="8">
         <v>0.53</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="E4" s="9">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="6">
         <v>48.3</v>
       </c>
       <c r="C5" s="7">
-        <v>1045.59</v>
+        <v>1045.5899999999999</v>
       </c>
       <c r="D5" s="8">
         <v>0.69</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="E5" s="9">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" s="6">
         <v>60.3</v>
@@ -637,24 +737,32 @@
       <c r="D6" s="8">
         <v>1.07</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="E6" s="9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="6">
-        <v>76.1</v>
-      </c>
-      <c r="C7" s="9">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="C7" s="10">
         <v>2595.598</v>
       </c>
       <c r="D7" s="8">
         <v>1.71</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="E7" s="9">
+        <f t="shared" si="0"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" s="6">
         <v>88.9</v>
@@ -665,10 +773,14 @@
       <c r="D8" s="8">
         <v>2.33</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="E8" s="9">
+        <f t="shared" si="0"/>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="6">
         <v>114.3</v>
@@ -679,24 +791,32 @@
       <c r="D9" s="8">
         <v>3.86</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="E9" s="9">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="6">
-        <v>139.7</v>
+        <v>139.69999999999999</v>
       </c>
       <c r="C10" s="7">
-        <v>8747.03</v>
+        <v>8747.0300000000007</v>
       </c>
       <c r="D10" s="8">
         <v>5.76</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="E10" s="9">
+        <f t="shared" si="0"/>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" s="6">
         <v>168.3</v>
@@ -705,12 +825,16 @@
         <v>12695.1</v>
       </c>
       <c r="D11" s="8">
-        <v>8.37</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75" customFormat="1" s="1">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="E11" s="9">
+        <f t="shared" si="0"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" s="6">
         <v>219.1</v>
@@ -721,12 +845,16 @@
       <c r="D12" s="8">
         <v>14.18</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="E12" s="9">
+        <f t="shared" si="0"/>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="10">
+        <v>16</v>
+      </c>
+      <c r="B13" s="11">
         <v>273</v>
       </c>
       <c r="C13" s="7">
@@ -735,13 +863,17 @@
       <c r="D13" s="8">
         <v>22.02</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="E13" s="9">
+        <f t="shared" si="0"/>
+        <v>441</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="6">
-        <v>323.9</v>
+        <v>323.89999999999998</v>
       </c>
       <c r="C14" s="7">
         <v>47020.81</v>
@@ -749,12 +881,16 @@
       <c r="D14" s="8">
         <v>30.99</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A15" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="12">
+      <c r="E14" s="9">
+        <f t="shared" si="0"/>
+        <v>579</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="13">
         <v>406.4</v>
       </c>
       <c r="C15" s="7">
@@ -762,6 +898,10 @@
       </c>
       <c r="D15" s="8">
         <v>48.79</v>
+      </c>
+      <c r="E15" s="9">
+        <f t="shared" si="0"/>
+        <v>849</v>
       </c>
     </row>
   </sheetData>

--- a/ressources/diametres.xlsx
+++ b/ressources/diametres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ecole\TEE\EnRezo\enRezo-Algorithm_steiner_V5.4\ressources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A27BA0FF-2DDF-4014-8669-882BF2FB29A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1F7C94-7136-4B37-8D3D-06FB2DAEB2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{7F82A3F0-3E44-46CE-BD27-2987FA7047D6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Diamètre Nominal (DN)</t>
   </si>
@@ -93,13 +93,22 @@
   </si>
   <si>
     <t>DN 400</t>
+  </si>
+  <si>
+    <t>DN 500</t>
+  </si>
+  <si>
+    <t>DN 450</t>
+  </si>
+  <si>
+    <t>DN 600</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,6 +147,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -157,7 +173,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -240,6 +256,21 @@
     </border>
     <border>
       <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right style="medium">
@@ -248,16 +279,67 @@
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -292,12 +374,38 @@
     <xf numFmtId="3" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -632,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E80D5BB7-3607-4563-BA5B-C588F8BE7E89}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" ht="25.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -660,13 +768,13 @@
         <v>26.9</v>
       </c>
       <c r="C2" s="7">
-        <v>324.3</v>
+        <v>181</v>
       </c>
       <c r="D2" s="8">
         <v>0.21</v>
       </c>
       <c r="E2" s="9">
-        <f t="shared" ref="E2:E15" si="0">ROUND(0.0042*B2^2 + 0.2056*B2 + 71.923, 0)</f>
+        <f t="shared" ref="E2:E18" si="0">ROUND(0.0042*B2^2 + 0.2056*B2 + 71.923, 0)</f>
         <v>80</v>
       </c>
     </row>
@@ -678,7 +786,7 @@
         <v>33.700000000000003</v>
       </c>
       <c r="C3" s="7">
-        <v>509.01</v>
+        <v>283</v>
       </c>
       <c r="D3" s="8">
         <v>0.33</v>
@@ -696,7 +804,7 @@
         <v>42.4</v>
       </c>
       <c r="C4" s="7">
-        <v>805.75</v>
+        <v>464</v>
       </c>
       <c r="D4" s="8">
         <v>0.53</v>
@@ -714,7 +822,7 @@
         <v>48.3</v>
       </c>
       <c r="C5" s="7">
-        <v>1045.5899999999999</v>
+        <v>725</v>
       </c>
       <c r="D5" s="8">
         <v>0.69</v>
@@ -732,7 +840,7 @@
         <v>60.3</v>
       </c>
       <c r="C6" s="7">
-        <v>1629.68</v>
+        <v>1132</v>
       </c>
       <c r="D6" s="8">
         <v>1.07</v>
@@ -750,7 +858,7 @@
         <v>76.099999999999994</v>
       </c>
       <c r="C7" s="10">
-        <v>2595.598</v>
+        <v>1914</v>
       </c>
       <c r="D7" s="8">
         <v>1.71</v>
@@ -768,7 +876,7 @@
         <v>88.9</v>
       </c>
       <c r="C8" s="7">
-        <v>3542.18</v>
+        <v>2900</v>
       </c>
       <c r="D8" s="8">
         <v>2.33</v>
@@ -786,7 +894,7 @@
         <v>114.3</v>
       </c>
       <c r="C9" s="7">
-        <v>5855.45</v>
+        <v>4531</v>
       </c>
       <c r="D9" s="8">
         <v>3.86</v>
@@ -804,7 +912,7 @@
         <v>139.69999999999999</v>
       </c>
       <c r="C10" s="7">
-        <v>8747.0300000000007</v>
+        <v>7080</v>
       </c>
       <c r="D10" s="8">
         <v>5.76</v>
@@ -822,7 +930,7 @@
         <v>168.3</v>
       </c>
       <c r="C11" s="7">
-        <v>12695.1</v>
+        <v>10195</v>
       </c>
       <c r="D11" s="8">
         <v>8.3699999999999992</v>
@@ -840,7 +948,7 @@
         <v>219.1</v>
       </c>
       <c r="C12" s="7">
-        <v>21515.57</v>
+        <v>18125</v>
       </c>
       <c r="D12" s="8">
         <v>14.18</v>
@@ -858,7 +966,7 @@
         <v>273</v>
       </c>
       <c r="C13" s="7">
-        <v>33403.61</v>
+        <v>28320</v>
       </c>
       <c r="D13" s="8">
         <v>22.02</v>
@@ -876,7 +984,7 @@
         <v>323.89999999999998</v>
       </c>
       <c r="C14" s="7">
-        <v>47020.81</v>
+        <v>40781</v>
       </c>
       <c r="D14" s="8">
         <v>30.99</v>
@@ -893,18 +1001,73 @@
       <c r="B15" s="13">
         <v>406.4</v>
       </c>
-      <c r="C15" s="7">
-        <v>74024.52</v>
-      </c>
-      <c r="D15" s="8">
+      <c r="C15" s="14">
+        <v>72500</v>
+      </c>
+      <c r="D15" s="15">
         <v>48.79</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="16">
         <f t="shared" si="0"/>
         <v>849</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="22">
+        <v>457.2</v>
+      </c>
+      <c r="C16" s="20">
+        <v>91758</v>
+      </c>
+      <c r="D16" s="22">
+        <v>59.83</v>
+      </c>
+      <c r="E16" s="18">
+        <f t="shared" si="0"/>
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="22">
+        <v>508</v>
+      </c>
+      <c r="C17" s="21">
+        <v>113281</v>
+      </c>
+      <c r="D17" s="22">
+        <v>73.87</v>
+      </c>
+      <c r="E17" s="19">
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="23">
+        <v>610</v>
+      </c>
+      <c r="C18" s="21">
+        <v>163126</v>
+      </c>
+      <c r="D18" s="23">
+        <v>106.37</v>
+      </c>
+      <c r="E18" s="19">
+        <f t="shared" si="0"/>
+        <v>1760</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>